--- a/data/raw/benv_exports/tubercolosi_bovina_2026_italia.xlsx
+++ b/data/raw/benv_exports/tubercolosi_bovina_2026_italia.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K120"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,22 +414,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>83015</v>
+        <v>83474</v>
       </c>
       <c r="B2" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C2" t="str">
         <v>E</v>
       </c>
       <c r="D2" t="str">
-        <v>18/03/2026</v>
+        <v>20/02/2026</v>
       </c>
       <c r="E2" t="str">
-        <v>19/01/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>27/05/2026</v>
+        <v>12/03/2026</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -438,18 +438,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I2" t="str">
-        <v>SAN LUCIDO</v>
+        <v>ARIANO NEL POLESINE</v>
       </c>
       <c r="J2" t="str">
-        <v>CS</v>
+        <v>RO</v>
       </c>
       <c r="K2" t="str">
-        <v>CALABRIA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>84200</v>
+        <v>83015</v>
       </c>
       <c r="B3" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -458,13 +458,13 @@
         <v>E</v>
       </c>
       <c r="D3" t="str">
-        <v>23/04/2026</v>
+        <v>18/03/2026</v>
       </c>
       <c r="E3" t="str">
-        <v>07/04/2026</v>
+        <v>19/01/2026</v>
       </c>
       <c r="F3" t="str">
-        <v>28/06/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -473,10 +473,10 @@
         <v>BOVINO</v>
       </c>
       <c r="I3" t="str">
-        <v>DRAPIA</v>
+        <v>SAN LUCIDO</v>
       </c>
       <c r="J3" t="str">
-        <v>VV</v>
+        <v>CS</v>
       </c>
       <c r="K3" t="str">
         <v>CALABRIA</v>
@@ -484,7 +484,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>84227</v>
+        <v>84200</v>
       </c>
       <c r="B4" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -493,13 +493,13 @@
         <v>E</v>
       </c>
       <c r="D4" t="str">
-        <v>08/05/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="E4" t="str">
-        <v>08/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="F4" t="str">
-        <v>29/06/2026</v>
+        <v>28/06/2026</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -508,10 +508,10 @@
         <v>BOVINO</v>
       </c>
       <c r="I4" t="str">
-        <v>ROGGIANO GRAVINA</v>
+        <v>DRAPIA</v>
       </c>
       <c r="J4" t="str">
-        <v>CS</v>
+        <v>VV</v>
       </c>
       <c r="K4" t="str">
         <v>CALABRIA</v>
@@ -519,7 +519,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>83334</v>
+        <v>84227</v>
       </c>
       <c r="B5" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -528,13 +528,13 @@
         <v>E</v>
       </c>
       <c r="D5" t="str">
-        <v>25/02/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="E5" t="str">
-        <v>13/02/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="F5" t="str">
-        <v>26/05/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -543,10 +543,10 @@
         <v>BOVINO</v>
       </c>
       <c r="I5" t="str">
-        <v>ROMBIOLO</v>
+        <v>ROGGIANO GRAVINA</v>
       </c>
       <c r="J5" t="str">
-        <v>VV</v>
+        <v>CS</v>
       </c>
       <c r="K5" t="str">
         <v>CALABRIA</v>
@@ -554,22 +554,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>82856</v>
+        <v>83834</v>
       </c>
       <c r="B6" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C6" t="str">
         <v>E</v>
       </c>
       <c r="D6" t="str">
-        <v>17/02/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="E6" t="str">
-        <v>14/01/2026</v>
+        <v>20/03/2026</v>
       </c>
       <c r="F6" t="str">
-        <v>18/05/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -578,10 +578,10 @@
         <v>BOVINO</v>
       </c>
       <c r="I6" t="str">
-        <v>PIGNATARO INTERAMNA</v>
+        <v>VALLINFREDA</v>
       </c>
       <c r="J6" t="str">
-        <v>FR</v>
+        <v>RM</v>
       </c>
       <c r="K6" t="str">
         <v>LAZIO</v>
@@ -589,22 +589,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>84415</v>
+        <v>82856</v>
       </c>
       <c r="B7" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C7" t="str">
         <v>E</v>
       </c>
       <c r="D7" t="str">
-        <v>27/04/2026</v>
+        <v>17/02/2026</v>
       </c>
       <c r="E7" t="str">
-        <v>27/04/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="F7" t="str">
-        <v>11/05/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -613,18 +613,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I7" t="str">
-        <v>MAIERATO</v>
+        <v>PIGNATARO INTERAMNA</v>
       </c>
       <c r="J7" t="str">
-        <v>VV</v>
+        <v>FR</v>
       </c>
       <c r="K7" t="str">
-        <v>CALABRIA</v>
+        <v>LAZIO</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>83274</v>
+        <v>83334</v>
       </c>
       <c r="B8" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -633,25 +633,25 @@
         <v>E</v>
       </c>
       <c r="D8" t="str">
-        <v>25/05/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="E8" t="str">
-        <v>09/02/2026</v>
+        <v>13/02/2026</v>
       </c>
       <c r="F8" t="str">
-        <v>27/05/2026</v>
+        <v>26/05/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>Mycobacterium tuberculosis complex</v>
+        <v/>
       </c>
       <c r="H8" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I8" t="str">
-        <v>BAGNARA CALABRA</v>
+        <v>ROMBIOLO</v>
       </c>
       <c r="J8" t="str">
-        <v>RC</v>
+        <v>VV</v>
       </c>
       <c r="K8" t="str">
         <v>CALABRIA</v>
@@ -659,22 +659,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>84262</v>
+        <v>84415</v>
       </c>
       <c r="B9" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C9" t="str">
         <v>E</v>
       </c>
       <c r="D9" t="str">
-        <v>22/04/2026</v>
+        <v>27/04/2026</v>
       </c>
       <c r="E9" t="str">
-        <v>16/04/2026</v>
+        <v>27/04/2026</v>
       </c>
       <c r="F9" t="str">
-        <v>10/07/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -683,18 +683,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I9" t="str">
-        <v>FERRANDINA</v>
+        <v>MAIERATO</v>
       </c>
       <c r="J9" t="str">
-        <v>MT</v>
+        <v>VV</v>
       </c>
       <c r="K9" t="str">
-        <v>BASILICATA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>83115</v>
+        <v>83274</v>
       </c>
       <c r="B10" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -703,48 +703,48 @@
         <v>E</v>
       </c>
       <c r="D10" t="str">
-        <v>17/04/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="E10" t="str">
-        <v>27/01/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="F10" t="str">
-        <v>06/07/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>Mycobacterium tuberculosis complex</v>
       </c>
       <c r="H10" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I10" t="str">
-        <v>PALAZZO ADRIANO</v>
+        <v>BAGNARA CALABRA</v>
       </c>
       <c r="J10" t="str">
-        <v>PA</v>
+        <v>RC</v>
       </c>
       <c r="K10" t="str">
-        <v>SICILIA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>83474</v>
+        <v>84072</v>
       </c>
       <c r="B11" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C11" t="str">
         <v>E</v>
       </c>
       <c r="D11" t="str">
-        <v>20/02/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="E11" t="str">
-        <v>16/02/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="F11" t="str">
-        <v>12/03/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -753,68 +753,68 @@
         <v>BOVINO</v>
       </c>
       <c r="I11" t="str">
-        <v>ARIANO NEL POLESINE</v>
+        <v>TOLVE</v>
       </c>
       <c r="J11" t="str">
-        <v>RO</v>
+        <v>PZ</v>
       </c>
       <c r="K11" t="str">
-        <v>VENETO</v>
+        <v>BASILICATA</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>84630</v>
+        <v>83426</v>
       </c>
       <c r="B12" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C12" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D12" t="str">
-        <v>12/06/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="E12" t="str">
-        <v>15/05/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="F12" t="str">
-        <v>-</v>
+        <v>14/07/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>Mycobacterium tuberculosis complex</v>
+        <v/>
       </c>
       <c r="H12" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I12" t="str">
-        <v>CALASCIBETTA</v>
+        <v>AMELIA</v>
       </c>
       <c r="J12" t="str">
-        <v>EN</v>
+        <v>TR</v>
       </c>
       <c r="K12" t="str">
-        <v>SICILIA</v>
+        <v>UMBRIA</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>84649</v>
+        <v>83942</v>
       </c>
       <c r="B13" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C13" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D13" t="str">
-        <v>18/05/2026</v>
+        <v>14/04/2026</v>
       </c>
       <c r="E13" t="str">
-        <v>18/05/2026</v>
+        <v>26/03/2026</v>
       </c>
       <c r="F13" t="str">
-        <v>-</v>
+        <v>21/07/2026</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -823,33 +823,33 @@
         <v>BOVINO</v>
       </c>
       <c r="I13" t="str">
-        <v>SERRA SAN QUIRICO</v>
+        <v>GRUMENTO NOVA</v>
       </c>
       <c r="J13" t="str">
-        <v>AN</v>
+        <v>PZ</v>
       </c>
       <c r="K13" t="str">
-        <v>MARCHE</v>
+        <v>BASILICATA</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>83049</v>
+        <v>84905</v>
       </c>
       <c r="B14" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C14" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D14" t="str">
-        <v>28/01/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="E14" t="str">
-        <v>20/01/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="F14" t="str">
-        <v>-</v>
+        <v>21/07/2026</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -858,33 +858,33 @@
         <v>BOVINO</v>
       </c>
       <c r="I14" t="str">
-        <v>ANGUILLARA SABAZIA</v>
+        <v>TURSI</v>
       </c>
       <c r="J14" t="str">
-        <v>RM</v>
+        <v>MT</v>
       </c>
       <c r="K14" t="str">
-        <v>LAZIO</v>
+        <v>BASILICATA</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>84082</v>
+        <v>84262</v>
       </c>
       <c r="B15" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C15" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D15" t="str">
-        <v>24/04/2026</v>
+        <v>22/04/2026</v>
       </c>
       <c r="E15" t="str">
-        <v>07/04/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="F15" t="str">
-        <v>-</v>
+        <v>10/07/2026</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -893,33 +893,33 @@
         <v>BOVINO</v>
       </c>
       <c r="I15" t="str">
-        <v>CANCELLO ED ARNONE</v>
+        <v>FERRANDINA</v>
       </c>
       <c r="J15" t="str">
-        <v>CE</v>
+        <v>MT</v>
       </c>
       <c r="K15" t="str">
-        <v>CAMPANIA</v>
+        <v>BASILICATA</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>85009</v>
+        <v>83115</v>
       </c>
       <c r="B16" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C16" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D16" t="str">
-        <v>16/06/2026</v>
+        <v>17/04/2026</v>
       </c>
       <c r="E16" t="str">
-        <v>08/06/2026</v>
+        <v>27/01/2026</v>
       </c>
       <c r="F16" t="str">
-        <v>-</v>
+        <v>06/07/2026</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -928,18 +928,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I16" t="str">
-        <v>CARPINONE</v>
+        <v>PALAZZO ADRIANO</v>
       </c>
       <c r="J16" t="str">
-        <v>IS</v>
+        <v>PA</v>
       </c>
       <c r="K16" t="str">
-        <v>MOLISE</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>85117</v>
+        <v>83835</v>
       </c>
       <c r="B17" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -948,10 +948,10 @@
         <v>C</v>
       </c>
       <c r="D17" t="str">
-        <v>19/06/2026</v>
+        <v>25/03/2026</v>
       </c>
       <c r="E17" t="str">
-        <v>16/06/2026</v>
+        <v>20/03/2026</v>
       </c>
       <c r="F17" t="str">
         <v>-</v>
@@ -963,30 +963,30 @@
         <v>BOVINO</v>
       </c>
       <c r="I17" t="str">
-        <v>BISEGNA</v>
+        <v>SPILINGA</v>
       </c>
       <c r="J17" t="str">
-        <v>AQ</v>
+        <v>VV</v>
       </c>
       <c r="K17" t="str">
-        <v>ABRUZZO</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>83215</v>
+        <v>83991</v>
       </c>
       <c r="B18" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C18" t="str">
         <v>C</v>
       </c>
       <c r="D18" t="str">
-        <v>14/05/2026</v>
+        <v>26/03/2026</v>
       </c>
       <c r="E18" t="str">
-        <v>02/02/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="F18" t="str">
         <v>-</v>
@@ -998,18 +998,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I18" t="str">
-        <v>NOTO</v>
+        <v>ROSCIGNO</v>
       </c>
       <c r="J18" t="str">
-        <v>SR</v>
+        <v>SA</v>
       </c>
       <c r="K18" t="str">
-        <v>SICILIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>83776</v>
+        <v>85099</v>
       </c>
       <c r="B19" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1018,10 +1018,10 @@
         <v>C</v>
       </c>
       <c r="D19" t="str">
-        <v>15/06/2026</v>
+        <v>17/06/2026</v>
       </c>
       <c r="E19" t="str">
-        <v>09/03/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="F19" t="str">
         <v>-</v>
@@ -1033,18 +1033,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I19" t="str">
-        <v>PIANA DEGLI ALBANESI</v>
+        <v>BISEGNA</v>
       </c>
       <c r="J19" t="str">
-        <v>PA</v>
+        <v>AQ</v>
       </c>
       <c r="K19" t="str">
-        <v>SICILIA</v>
+        <v>ABRUZZO</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>83601</v>
+        <v>82879</v>
       </c>
       <c r="B20" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -1053,10 +1053,10 @@
         <v>C</v>
       </c>
       <c r="D20" t="str">
-        <v>26/02/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="E20" t="str">
-        <v>11/02/2026</v>
+        <v>16/01/2026</v>
       </c>
       <c r="F20" t="str">
         <v>-</v>
@@ -1068,18 +1068,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I20" t="str">
-        <v>GIFFONI VALLE PIANA</v>
+        <v>RAGUSA</v>
       </c>
       <c r="J20" t="str">
-        <v>SA</v>
+        <v>RG</v>
       </c>
       <c r="K20" t="str">
-        <v>CAMPANIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>84394</v>
+        <v>85027</v>
       </c>
       <c r="B21" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1088,45 +1088,45 @@
         <v>C</v>
       </c>
       <c r="D21" t="str">
-        <v>22/05/2026</v>
+        <v>10/06/2026</v>
       </c>
       <c r="E21" t="str">
-        <v>21/04/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="F21" t="str">
         <v>-</v>
       </c>
       <c r="G21" t="str">
-        <v>Mycobacterium tuberculosis complex</v>
+        <v/>
       </c>
       <c r="H21" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I21" t="str">
-        <v>SAN GIOVANNI ROTONDO</v>
+        <v>MOLITERNO</v>
       </c>
       <c r="J21" t="str">
-        <v>FG</v>
+        <v>PZ</v>
       </c>
       <c r="K21" t="str">
-        <v>PUGLIA</v>
+        <v>BASILICATA</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>84274</v>
+        <v>85098</v>
       </c>
       <c r="B22" t="str">
-        <v>FOCOLAIO CLINICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C22" t="str">
         <v>C</v>
       </c>
       <c r="D22" t="str">
-        <v>24/04/2026</v>
+        <v>17/06/2026</v>
       </c>
       <c r="E22" t="str">
-        <v>16/04/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="F22" t="str">
         <v>-</v>
@@ -1138,18 +1138,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I22" t="str">
-        <v>SIRACUSA</v>
+        <v>BISEGNA</v>
       </c>
       <c r="J22" t="str">
-        <v>SR</v>
+        <v>AQ</v>
       </c>
       <c r="K22" t="str">
-        <v>SICILIA</v>
+        <v>ABRUZZO</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>83921</v>
+        <v>82900</v>
       </c>
       <c r="B23" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1158,10 +1158,10 @@
         <v>C</v>
       </c>
       <c r="D23" t="str">
-        <v>20/05/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="E23" t="str">
-        <v>17/03/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="F23" t="str">
         <v>-</v>
@@ -1173,30 +1173,30 @@
         <v>BOVINO</v>
       </c>
       <c r="I23" t="str">
-        <v>CASTELDACCIA</v>
+        <v>CELLE DI BULGHERIA</v>
       </c>
       <c r="J23" t="str">
-        <v>PA</v>
+        <v>SA</v>
       </c>
       <c r="K23" t="str">
-        <v>SICILIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>83750</v>
+        <v>84226</v>
       </c>
       <c r="B24" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C24" t="str">
         <v>C</v>
       </c>
       <c r="D24" t="str">
-        <v>20/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="E24" t="str">
-        <v>13/03/2026</v>
+        <v>14/04/2026</v>
       </c>
       <c r="F24" t="str">
         <v>-</v>
@@ -1208,18 +1208,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I24" t="str">
-        <v>CACCAMO</v>
+        <v>MORETTA</v>
       </c>
       <c r="J24" t="str">
-        <v>PA</v>
+        <v>CN</v>
       </c>
       <c r="K24" t="str">
-        <v>SICILIA</v>
+        <v>PIEMONTE</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>83556</v>
+        <v>83165</v>
       </c>
       <c r="B25" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1228,68 +1228,68 @@
         <v>C</v>
       </c>
       <c r="D25" t="str">
-        <v>22/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="E25" t="str">
-        <v>23/02/2026</v>
+        <v>29/01/2026</v>
       </c>
       <c r="F25" t="str">
         <v>-</v>
       </c>
       <c r="G25" t="str">
-        <v>Mycobacterium bovis</v>
+        <v>Mycobacterium tuberculosis complex</v>
       </c>
       <c r="H25" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I25" t="str">
-        <v>SASSOFERRATO</v>
+        <v>BRUZZANO ZEFFIRIO</v>
       </c>
       <c r="J25" t="str">
-        <v>AN</v>
+        <v>RC</v>
       </c>
       <c r="K25" t="str">
-        <v>MARCHE</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>85193</v>
+        <v>84022</v>
       </c>
       <c r="B26" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C26" t="str">
         <v>C</v>
       </c>
       <c r="D26" t="str">
-        <v>01/07/2026</v>
+        <v>26/05/2026</v>
       </c>
       <c r="E26" t="str">
-        <v>19/06/2026</v>
+        <v>20/03/2026</v>
       </c>
       <c r="F26" t="str">
         <v>-</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>Mycobacterium bovis</v>
       </c>
       <c r="H26" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I26" t="str">
-        <v>SAN CALOGERO</v>
+        <v>CALTAGIRONE</v>
       </c>
       <c r="J26" t="str">
-        <v>VV</v>
+        <v>CT</v>
       </c>
       <c r="K26" t="str">
-        <v>CALABRIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>83506</v>
+        <v>84085</v>
       </c>
       <c r="B27" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1298,45 +1298,45 @@
         <v>C</v>
       </c>
       <c r="D27" t="str">
-        <v>10/03/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="E27" t="str">
-        <v>21/02/2026</v>
+        <v>02/04/2026</v>
       </c>
       <c r="F27" t="str">
         <v>-</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>Mycobacterium bovis</v>
       </c>
       <c r="H27" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I27" t="str">
-        <v>CAMERINO</v>
+        <v>BRUZZANO ZEFFIRIO</v>
       </c>
       <c r="J27" t="str">
-        <v>MC</v>
+        <v>RC</v>
       </c>
       <c r="K27" t="str">
-        <v>MARCHE</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>84272</v>
+        <v>84093</v>
       </c>
       <c r="B28" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C28" t="str">
         <v>C</v>
       </c>
       <c r="D28" t="str">
-        <v>31/05/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="E28" t="str">
-        <v>17/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="F28" t="str">
         <v>-</v>
@@ -1348,18 +1348,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I28" t="str">
-        <v>CALTABELLOTTA</v>
+        <v>GIFFONI VALLE PIANA</v>
       </c>
       <c r="J28" t="str">
-        <v>AG</v>
+        <v>SA</v>
       </c>
       <c r="K28" t="str">
-        <v>SICILIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>84360</v>
+        <v>85009</v>
       </c>
       <c r="B29" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1368,45 +1368,45 @@
         <v>C</v>
       </c>
       <c r="D29" t="str">
-        <v>22/05/2026</v>
+        <v>16/06/2026</v>
       </c>
       <c r="E29" t="str">
-        <v>21/04/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="F29" t="str">
         <v>-</v>
       </c>
       <c r="G29" t="str">
-        <v>Mycobacterium tuberculosis complex</v>
+        <v/>
       </c>
       <c r="H29" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I29" t="str">
-        <v>SAN GIOVANNI ROTONDO</v>
+        <v>CARPINONE</v>
       </c>
       <c r="J29" t="str">
-        <v>FG</v>
+        <v>IS</v>
       </c>
       <c r="K29" t="str">
-        <v>PUGLIA</v>
+        <v>MOLISE</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>83262</v>
+        <v>85117</v>
       </c>
       <c r="B30" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C30" t="str">
         <v>C</v>
       </c>
       <c r="D30" t="str">
-        <v>10/03/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="E30" t="str">
-        <v>06/02/2026</v>
+        <v>16/06/2026</v>
       </c>
       <c r="F30" t="str">
         <v>-</v>
@@ -1418,65 +1418,65 @@
         <v>BOVINO</v>
       </c>
       <c r="I30" t="str">
-        <v>VERZINO</v>
+        <v>BISEGNA</v>
       </c>
       <c r="J30" t="str">
-        <v>KR</v>
+        <v>AQ</v>
       </c>
       <c r="K30" t="str">
-        <v>CALABRIA</v>
+        <v>ABRUZZO</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>83299</v>
+        <v>85499</v>
       </c>
       <c r="B31" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C31" t="str">
         <v>C</v>
       </c>
       <c r="D31" t="str">
-        <v>10/03/2026</v>
+        <v>07/05/2026</v>
       </c>
       <c r="E31" t="str">
-        <v>21/01/2026</v>
+        <v>07/05/2026</v>
       </c>
       <c r="F31" t="str">
         <v>-</v>
       </c>
       <c r="G31" t="str">
-        <v>Mycobacterium bovis</v>
+        <v/>
       </c>
       <c r="H31" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I31" t="str">
-        <v>TORTORICI</v>
+        <v>MATELICA</v>
       </c>
       <c r="J31" t="str">
-        <v>ME</v>
+        <v>MC</v>
       </c>
       <c r="K31" t="str">
-        <v>SICILIA</v>
+        <v>MARCHE</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>84090</v>
+        <v>85233</v>
       </c>
       <c r="B32" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C32" t="str">
         <v>C</v>
       </c>
       <c r="D32" t="str">
-        <v>20/04/2026</v>
+        <v>18/07/2026</v>
       </c>
       <c r="E32" t="str">
-        <v>03/04/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="F32" t="str">
         <v>-</v>
@@ -1488,7 +1488,7 @@
         <v>BOVINO</v>
       </c>
       <c r="I32" t="str">
-        <v>SERRE</v>
+        <v>GIFFONI VALLE PIANA</v>
       </c>
       <c r="J32" t="str">
         <v>SA</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>83958</v>
+        <v>85690</v>
       </c>
       <c r="B33" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -1508,10 +1508,10 @@
         <v>C</v>
       </c>
       <c r="D33" t="str">
-        <v>31/03/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="E33" t="str">
-        <v>25/03/2026</v>
+        <v>16/07/2026</v>
       </c>
       <c r="F33" t="str">
         <v>-</v>
@@ -1523,18 +1523,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I33" t="str">
-        <v>PUTIGNANO</v>
+        <v>EBOLI</v>
       </c>
       <c r="J33" t="str">
-        <v>BA</v>
+        <v>SA</v>
       </c>
       <c r="K33" t="str">
-        <v>PUGLIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>84823</v>
+        <v>84630</v>
       </c>
       <c r="B34" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1543,80 +1543,80 @@
         <v>C</v>
       </c>
       <c r="D34" t="str">
-        <v>01/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="E34" t="str">
-        <v>25/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="F34" t="str">
         <v>-</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>Mycobacterium tuberculosis complex</v>
       </c>
       <c r="H34" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I34" t="str">
-        <v>SAN LORENZO BELLIZZI</v>
+        <v>CALASCIBETTA</v>
       </c>
       <c r="J34" t="str">
-        <v>CS</v>
+        <v>EN</v>
       </c>
       <c r="K34" t="str">
-        <v>CALABRIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>83968</v>
+        <v>84632</v>
       </c>
       <c r="B35" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C35" t="str">
         <v>C</v>
       </c>
       <c r="D35" t="str">
-        <v>27/04/2026</v>
+        <v>21/07/2026</v>
       </c>
       <c r="E35" t="str">
-        <v>27/03/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="F35" t="str">
         <v>-</v>
       </c>
       <c r="G35" t="str">
-        <v/>
+        <v>Mycobacterium bovis</v>
       </c>
       <c r="H35" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I35" t="str">
-        <v>TREIA</v>
+        <v>BRONTE</v>
       </c>
       <c r="J35" t="str">
-        <v>MC</v>
+        <v>CT</v>
       </c>
       <c r="K35" t="str">
-        <v>MARCHE</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>84887</v>
+        <v>83049</v>
       </c>
       <c r="B36" t="str">
-        <v>FOCOLAIO CLINICO</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C36" t="str">
         <v>C</v>
       </c>
       <c r="D36" t="str">
-        <v>10/06/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="E36" t="str">
-        <v>29/05/2026</v>
+        <v>20/01/2026</v>
       </c>
       <c r="F36" t="str">
         <v>-</v>
@@ -1628,18 +1628,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I36" t="str">
-        <v>VIETRI SUL MARE</v>
+        <v>ANGUILLARA SABAZIA</v>
       </c>
       <c r="J36" t="str">
-        <v>SA</v>
+        <v>RM</v>
       </c>
       <c r="K36" t="str">
-        <v>CAMPANIA</v>
+        <v>LAZIO</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>84905</v>
+        <v>85331</v>
       </c>
       <c r="B37" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1648,10 +1648,10 @@
         <v>C</v>
       </c>
       <c r="D37" t="str">
-        <v>02/07/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="E37" t="str">
-        <v>28/05/2026</v>
+        <v>13/06/2026</v>
       </c>
       <c r="F37" t="str">
         <v>-</v>
@@ -1663,18 +1663,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I37" t="str">
-        <v>TURSI</v>
+        <v>UMBRIATICO</v>
       </c>
       <c r="J37" t="str">
-        <v>MT</v>
+        <v>KR</v>
       </c>
       <c r="K37" t="str">
-        <v>BASILICATA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>83376</v>
+        <v>83215</v>
       </c>
       <c r="B38" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -1683,10 +1683,10 @@
         <v>C</v>
       </c>
       <c r="D38" t="str">
-        <v>23/02/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="E38" t="str">
-        <v>16/02/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="F38" t="str">
         <v>-</v>
@@ -1698,18 +1698,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I38" t="str">
-        <v>MONTEROSSO CALABRO</v>
+        <v>NOTO</v>
       </c>
       <c r="J38" t="str">
-        <v>VV</v>
+        <v>SR</v>
       </c>
       <c r="K38" t="str">
-        <v>CALABRIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>83490</v>
+        <v>83776</v>
       </c>
       <c r="B39" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1718,10 +1718,10 @@
         <v>C</v>
       </c>
       <c r="D39" t="str">
-        <v>10/03/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="E39" t="str">
-        <v>25/02/2026</v>
+        <v>09/03/2026</v>
       </c>
       <c r="F39" t="str">
         <v>-</v>
@@ -1733,18 +1733,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I39" t="str">
-        <v>SASSANO</v>
+        <v>PIANA DEGLI ALBANESI</v>
       </c>
       <c r="J39" t="str">
-        <v>SA</v>
+        <v>PA</v>
       </c>
       <c r="K39" t="str">
-        <v>CAMPANIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>84230</v>
+        <v>83601</v>
       </c>
       <c r="B40" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -1753,10 +1753,10 @@
         <v>C</v>
       </c>
       <c r="D40" t="str">
-        <v>13/05/2026</v>
+        <v>26/02/2026</v>
       </c>
       <c r="E40" t="str">
-        <v>13/04/2026</v>
+        <v>11/02/2026</v>
       </c>
       <c r="F40" t="str">
         <v>-</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>84281</v>
+        <v>85159</v>
       </c>
       <c r="B41" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1788,33 +1788,33 @@
         <v>C</v>
       </c>
       <c r="D41" t="str">
-        <v>26/06/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="E41" t="str">
-        <v>17/04/2026</v>
+        <v>17/06/2026</v>
       </c>
       <c r="F41" t="str">
         <v>-</v>
       </c>
       <c r="G41" t="str">
-        <v>Mycobacterium bovis</v>
+        <v/>
       </c>
       <c r="H41" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I41" t="str">
-        <v>CONDOFURI</v>
+        <v>SAN NICANDRO GARGANICO</v>
       </c>
       <c r="J41" t="str">
-        <v>RC</v>
+        <v>FG</v>
       </c>
       <c r="K41" t="str">
-        <v>CALABRIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>84639</v>
+        <v>84394</v>
       </c>
       <c r="B42" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1823,33 +1823,33 @@
         <v>C</v>
       </c>
       <c r="D42" t="str">
-        <v>03/06/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="E42" t="str">
-        <v>15/05/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="F42" t="str">
         <v>-</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>Mycobacterium tuberculosis complex</v>
       </c>
       <c r="H42" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I42" t="str">
-        <v>GIFFONI VALLE PIANA</v>
+        <v>SAN GIOVANNI ROTONDO</v>
       </c>
       <c r="J42" t="str">
-        <v>SA</v>
+        <v>FG</v>
       </c>
       <c r="K42" t="str">
-        <v>CAMPANIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>84055</v>
+        <v>83921</v>
       </c>
       <c r="B43" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1858,25 +1858,25 @@
         <v>C</v>
       </c>
       <c r="D43" t="str">
-        <v>06/05/2026</v>
+        <v>20/05/2026</v>
       </c>
       <c r="E43" t="str">
-        <v>02/04/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="F43" t="str">
         <v>-</v>
       </c>
       <c r="G43" t="str">
-        <v>Mycobacterium tuberculosis complex</v>
+        <v/>
       </c>
       <c r="H43" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I43" t="str">
-        <v>LEONFORTE</v>
+        <v>CASTELDACCIA</v>
       </c>
       <c r="J43" t="str">
-        <v>EN</v>
+        <v>PA</v>
       </c>
       <c r="K43" t="str">
         <v>SICILIA</v>
@@ -1884,7 +1884,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>84005</v>
+        <v>83750</v>
       </c>
       <c r="B44" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1893,33 +1893,33 @@
         <v>C</v>
       </c>
       <c r="D44" t="str">
-        <v>26/06/2026</v>
+        <v>20/05/2026</v>
       </c>
       <c r="E44" t="str">
-        <v>27/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="F44" t="str">
         <v>-</v>
       </c>
       <c r="G44" t="str">
-        <v>Mycobacterium bovis</v>
+        <v/>
       </c>
       <c r="H44" t="str">
-        <v>BUFALO</v>
+        <v>BOVINO</v>
       </c>
       <c r="I44" t="str">
-        <v>ISOLA DI CAPO RIZZUTO</v>
+        <v>CACCAMO</v>
       </c>
       <c r="J44" t="str">
-        <v>KR</v>
+        <v>PA</v>
       </c>
       <c r="K44" t="str">
-        <v>CALABRIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>82866</v>
+        <v>83556</v>
       </c>
       <c r="B45" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1928,10 +1928,10 @@
         <v>C</v>
       </c>
       <c r="D45" t="str">
-        <v>23/03/2026</v>
+        <v>22/04/2026</v>
       </c>
       <c r="E45" t="str">
-        <v>15/01/2026</v>
+        <v>23/02/2026</v>
       </c>
       <c r="F45" t="str">
         <v>-</v>
@@ -1943,30 +1943,30 @@
         <v>BOVINO</v>
       </c>
       <c r="I45" t="str">
-        <v>CALTAGIRONE</v>
+        <v>SASSOFERRATO</v>
       </c>
       <c r="J45" t="str">
-        <v>CT</v>
+        <v>AN</v>
       </c>
       <c r="K45" t="str">
-        <v>SICILIA</v>
+        <v>MARCHE</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>83650</v>
+        <v>85193</v>
       </c>
       <c r="B46" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C46" t="str">
         <v>C</v>
       </c>
       <c r="D46" t="str">
-        <v>22/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="E46" t="str">
-        <v>07/03/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="F46" t="str">
         <v>-</v>
@@ -1975,33 +1975,33 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>BUFALO</v>
+        <v>BOVINO</v>
       </c>
       <c r="I46" t="str">
-        <v>CANCELLO ED ARNONE</v>
+        <v>SAN CALOGERO</v>
       </c>
       <c r="J46" t="str">
-        <v>CE</v>
+        <v>VV</v>
       </c>
       <c r="K46" t="str">
-        <v>CAMPANIA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>84231</v>
+        <v>84274</v>
       </c>
       <c r="B47" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C47" t="str">
         <v>C</v>
       </c>
       <c r="D47" t="str">
-        <v>13/05/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="E47" t="str">
-        <v>13/04/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="F47" t="str">
         <v>-</v>
@@ -2013,18 +2013,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I47" t="str">
-        <v>GIFFONI VALLE PIANA</v>
+        <v>SIRACUSA</v>
       </c>
       <c r="J47" t="str">
-        <v>SA</v>
+        <v>SR</v>
       </c>
       <c r="K47" t="str">
-        <v>CAMPANIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>85029</v>
+        <v>83506</v>
       </c>
       <c r="B48" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -2033,10 +2033,10 @@
         <v>C</v>
       </c>
       <c r="D48" t="str">
-        <v>29/06/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="E48" t="str">
-        <v>09/06/2026</v>
+        <v>21/02/2026</v>
       </c>
       <c r="F48" t="str">
         <v>-</v>
@@ -2048,30 +2048,30 @@
         <v>BOVINO</v>
       </c>
       <c r="I48" t="str">
-        <v>SANZA</v>
+        <v>CAMERINO</v>
       </c>
       <c r="J48" t="str">
-        <v>SA</v>
+        <v>MC</v>
       </c>
       <c r="K48" t="str">
-        <v>CAMPANIA</v>
+        <v>MARCHE</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>85111</v>
+        <v>84272</v>
       </c>
       <c r="B49" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C49" t="str">
         <v>C</v>
       </c>
       <c r="D49" t="str">
-        <v>26/06/2026</v>
+        <v>31/05/2026</v>
       </c>
       <c r="E49" t="str">
-        <v>15/06/2026</v>
+        <v>17/04/2026</v>
       </c>
       <c r="F49" t="str">
         <v>-</v>
@@ -2083,18 +2083,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I49" t="str">
-        <v>CERASO</v>
+        <v>CALTABELLOTTA</v>
       </c>
       <c r="J49" t="str">
-        <v>SA</v>
+        <v>AG</v>
       </c>
       <c r="K49" t="str">
-        <v>CAMPANIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>85456</v>
+        <v>84360</v>
       </c>
       <c r="B50" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -2103,45 +2103,45 @@
         <v>C</v>
       </c>
       <c r="D50" t="str">
-        <v>08/07/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="E50" t="str">
-        <v>02/07/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="F50" t="str">
         <v>-</v>
       </c>
       <c r="G50" t="str">
-        <v/>
+        <v>Mycobacterium tuberculosis complex</v>
       </c>
       <c r="H50" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I50" t="str">
-        <v>SANT\'ONOFRIO</v>
+        <v>SAN GIOVANNI ROTONDO</v>
       </c>
       <c r="J50" t="str">
-        <v>VV</v>
+        <v>FG</v>
       </c>
       <c r="K50" t="str">
-        <v>CALABRIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>84422</v>
+        <v>83262</v>
       </c>
       <c r="B51" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C51" t="str">
         <v>C</v>
       </c>
       <c r="D51" t="str">
-        <v>16/05/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="E51" t="str">
-        <v>24/04/2026</v>
+        <v>06/02/2026</v>
       </c>
       <c r="F51" t="str">
         <v>-</v>
@@ -2153,45 +2153,45 @@
         <v>BOVINO</v>
       </c>
       <c r="I51" t="str">
-        <v>MATELICA</v>
+        <v>VERZINO</v>
       </c>
       <c r="J51" t="str">
-        <v>MC</v>
+        <v>KR</v>
       </c>
       <c r="K51" t="str">
-        <v>MARCHE</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>83405</v>
+        <v>83299</v>
       </c>
       <c r="B52" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C52" t="str">
         <v>C</v>
       </c>
       <c r="D52" t="str">
-        <v>19/02/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="E52" t="str">
-        <v>16/02/2026</v>
+        <v>21/01/2026</v>
       </c>
       <c r="F52" t="str">
         <v>-</v>
       </c>
       <c r="G52" t="str">
-        <v/>
+        <v>Mycobacterium bovis</v>
       </c>
       <c r="H52" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I52" t="str">
-        <v>CIMINNA</v>
+        <v>TORTORICI</v>
       </c>
       <c r="J52" t="str">
-        <v>PA</v>
+        <v>ME</v>
       </c>
       <c r="K52" t="str">
         <v>SICILIA</v>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>84533</v>
+        <v>84090</v>
       </c>
       <c r="B53" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -2208,33 +2208,33 @@
         <v>C</v>
       </c>
       <c r="D53" t="str">
-        <v>28/05/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="E53" t="str">
-        <v>08/05/2026</v>
+        <v>03/04/2026</v>
       </c>
       <c r="F53" t="str">
         <v>-</v>
       </c>
       <c r="G53" t="str">
-        <v>Mycobacterium tuberculosis complex</v>
+        <v/>
       </c>
       <c r="H53" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I53" t="str">
-        <v>CENTURIPE</v>
+        <v>SERRE</v>
       </c>
       <c r="J53" t="str">
-        <v>EN</v>
+        <v>SA</v>
       </c>
       <c r="K53" t="str">
-        <v>SICILIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>83364</v>
+        <v>83958</v>
       </c>
       <c r="B54" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -2243,45 +2243,45 @@
         <v>C</v>
       </c>
       <c r="D54" t="str">
-        <v>12/03/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="E54" t="str">
-        <v>13/02/2026</v>
+        <v>25/03/2026</v>
       </c>
       <c r="F54" t="str">
         <v>-</v>
       </c>
       <c r="G54" t="str">
-        <v>Mycobacterium tuberculosis complex</v>
+        <v/>
       </c>
       <c r="H54" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I54" t="str">
-        <v>NICOSIA</v>
+        <v>PUTIGNANO</v>
       </c>
       <c r="J54" t="str">
-        <v>EN</v>
+        <v>BA</v>
       </c>
       <c r="K54" t="str">
-        <v>SICILIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>83426</v>
+        <v>84823</v>
       </c>
       <c r="B55" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C55" t="str">
         <v>C</v>
       </c>
       <c r="D55" t="str">
-        <v>24/02/2026</v>
+        <v>01/06/2026</v>
       </c>
       <c r="E55" t="str">
-        <v>19/02/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="F55" t="str">
         <v>-</v>
@@ -2293,18 +2293,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I55" t="str">
-        <v>AMELIA</v>
+        <v>SAN LORENZO BELLIZZI</v>
       </c>
       <c r="J55" t="str">
-        <v>TR</v>
+        <v>CS</v>
       </c>
       <c r="K55" t="str">
-        <v>UMBRIA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>84047</v>
+        <v>83968</v>
       </c>
       <c r="B56" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -2313,10 +2313,10 @@
         <v>C</v>
       </c>
       <c r="D56" t="str">
-        <v>12/06/2026</v>
+        <v>27/04/2026</v>
       </c>
       <c r="E56" t="str">
-        <v>30/03/2026</v>
+        <v>27/03/2026</v>
       </c>
       <c r="F56" t="str">
         <v>-</v>
@@ -2328,30 +2328,30 @@
         <v>BOVINO</v>
       </c>
       <c r="I56" t="str">
-        <v>MODICA</v>
+        <v>TREIA</v>
       </c>
       <c r="J56" t="str">
-        <v>RG</v>
+        <v>MC</v>
       </c>
       <c r="K56" t="str">
-        <v>SICILIA</v>
+        <v>MARCHE</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>85125</v>
+        <v>84887</v>
       </c>
       <c r="B57" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C57" t="str">
         <v>C</v>
       </c>
       <c r="D57" t="str">
-        <v>17/06/2026</v>
+        <v>10/06/2026</v>
       </c>
       <c r="E57" t="str">
-        <v>17/06/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="F57" t="str">
         <v>-</v>
@@ -2363,18 +2363,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I57" t="str">
-        <v>TROINA</v>
+        <v>VIETRI SUL MARE</v>
       </c>
       <c r="J57" t="str">
-        <v>EN</v>
+        <v>SA</v>
       </c>
       <c r="K57" t="str">
-        <v>SICILIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>83823</v>
+        <v>83376</v>
       </c>
       <c r="B58" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -2383,10 +2383,10 @@
         <v>C</v>
       </c>
       <c r="D58" t="str">
-        <v>10/04/2026</v>
+        <v>23/02/2026</v>
       </c>
       <c r="E58" t="str">
-        <v>19/03/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="F58" t="str">
         <v>-</v>
@@ -2398,18 +2398,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I58" t="str">
-        <v>BORGO SAN LORENZO</v>
+        <v>MONTEROSSO CALABRO</v>
       </c>
       <c r="J58" t="str">
-        <v>FI</v>
+        <v>VV</v>
       </c>
       <c r="K58" t="str">
-        <v>TOSCANA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>83227</v>
+        <v>83490</v>
       </c>
       <c r="B59" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -2418,33 +2418,33 @@
         <v>C</v>
       </c>
       <c r="D59" t="str">
-        <v>02/02/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="E59" t="str">
-        <v>23/01/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="F59" t="str">
         <v>-</v>
       </c>
       <c r="G59" t="str">
-        <v>Mycobacterium bovis</v>
+        <v/>
       </c>
       <c r="H59" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I59" t="str">
-        <v>ROMBIOLO</v>
+        <v>SASSANO</v>
       </c>
       <c r="J59" t="str">
-        <v>VV</v>
+        <v>SA</v>
       </c>
       <c r="K59" t="str">
-        <v>CALABRIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>85031</v>
+        <v>84230</v>
       </c>
       <c r="B60" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -2453,10 +2453,10 @@
         <v>C</v>
       </c>
       <c r="D60" t="str">
-        <v>19/06/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="E60" t="str">
-        <v>09/06/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="F60" t="str">
         <v>-</v>
@@ -2468,18 +2468,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I60" t="str">
-        <v>MESORACA</v>
+        <v>GIFFONI VALLE PIANA</v>
       </c>
       <c r="J60" t="str">
-        <v>KR</v>
+        <v>SA</v>
       </c>
       <c r="K60" t="str">
-        <v>CALABRIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>84855</v>
+        <v>84281</v>
       </c>
       <c r="B61" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -2488,80 +2488,80 @@
         <v>C</v>
       </c>
       <c r="D61" t="str">
-        <v>10/06/2026</v>
+        <v>26/06/2026</v>
       </c>
       <c r="E61" t="str">
-        <v>27/05/2026</v>
+        <v>17/04/2026</v>
       </c>
       <c r="F61" t="str">
         <v>-</v>
       </c>
       <c r="G61" t="str">
-        <v/>
+        <v>Mycobacterium bovis</v>
       </c>
       <c r="H61" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I61" t="str">
-        <v>PISCIOTTA</v>
+        <v>CONDOFURI</v>
       </c>
       <c r="J61" t="str">
-        <v>SA</v>
+        <v>RC</v>
       </c>
       <c r="K61" t="str">
-        <v>CAMPANIA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>83774</v>
+        <v>84649</v>
       </c>
       <c r="B62" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C62" t="str">
         <v>C</v>
       </c>
       <c r="D62" t="str">
-        <v>16/04/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="E62" t="str">
-        <v>16/03/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="F62" t="str">
         <v>-</v>
       </c>
       <c r="G62" t="str">
-        <v/>
+        <v>Mycobacterium bovis</v>
       </c>
       <c r="H62" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I62" t="str">
-        <v>AGIRA</v>
+        <v>SERRA SAN QUIRICO</v>
       </c>
       <c r="J62" t="str">
-        <v>EN</v>
+        <v>AN</v>
       </c>
       <c r="K62" t="str">
-        <v>SICILIA</v>
+        <v>MARCHE</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>84275</v>
+        <v>84639</v>
       </c>
       <c r="B63" t="str">
-        <v>FOCOLAIO CLINICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C63" t="str">
         <v>C</v>
       </c>
       <c r="D63" t="str">
-        <v>30/04/2026</v>
+        <v>03/06/2026</v>
       </c>
       <c r="E63" t="str">
-        <v>17/04/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="F63" t="str">
         <v>-</v>
@@ -2573,18 +2573,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I63" t="str">
-        <v>SIRACUSA</v>
+        <v>GIFFONI VALLE PIANA</v>
       </c>
       <c r="J63" t="str">
-        <v>SR</v>
+        <v>SA</v>
       </c>
       <c r="K63" t="str">
-        <v>SICILIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>84668</v>
+        <v>84055</v>
       </c>
       <c r="B64" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -2593,10 +2593,10 @@
         <v>C</v>
       </c>
       <c r="D64" t="str">
-        <v>19/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="E64" t="str">
-        <v>19/05/2026</v>
+        <v>02/04/2026</v>
       </c>
       <c r="F64" t="str">
         <v>-</v>
@@ -2608,88 +2608,88 @@
         <v>BOVINO</v>
       </c>
       <c r="I64" t="str">
-        <v>PAZZANO</v>
+        <v>LEONFORTE</v>
       </c>
       <c r="J64" t="str">
-        <v>RC</v>
+        <v>EN</v>
       </c>
       <c r="K64" t="str">
-        <v>CALABRIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>83190</v>
+        <v>84005</v>
       </c>
       <c r="B65" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C65" t="str">
         <v>C</v>
       </c>
       <c r="D65" t="str">
-        <v>27/05/2026</v>
+        <v>26/06/2026</v>
       </c>
       <c r="E65" t="str">
-        <v>03/02/2026</v>
+        <v>27/03/2026</v>
       </c>
       <c r="F65" t="str">
         <v>-</v>
       </c>
       <c r="G65" t="str">
-        <v/>
+        <v>Mycobacterium bovis</v>
       </c>
       <c r="H65" t="str">
-        <v>BOVINO</v>
+        <v>BUFALO</v>
       </c>
       <c r="I65" t="str">
-        <v>MODICA</v>
+        <v>ISOLA DI CAPO RIZZUTO</v>
       </c>
       <c r="J65" t="str">
-        <v>RG</v>
+        <v>KR</v>
       </c>
       <c r="K65" t="str">
-        <v>SICILIA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>83591</v>
+        <v>82866</v>
       </c>
       <c r="B66" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C66" t="str">
         <v>C</v>
       </c>
       <c r="D66" t="str">
-        <v>09/03/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="E66" t="str">
-        <v>03/02/2026</v>
+        <v>15/01/2026</v>
       </c>
       <c r="F66" t="str">
         <v>-</v>
       </c>
       <c r="G66" t="str">
-        <v/>
+        <v>Mycobacterium bovis</v>
       </c>
       <c r="H66" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I66" t="str">
-        <v>VOLTURARA IRPINA</v>
+        <v>CALTAGIRONE</v>
       </c>
       <c r="J66" t="str">
-        <v>AV</v>
+        <v>CT</v>
       </c>
       <c r="K66" t="str">
-        <v>CAMPANIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>83526</v>
+        <v>83650</v>
       </c>
       <c r="B67" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -2698,10 +2698,10 @@
         <v>C</v>
       </c>
       <c r="D67" t="str">
-        <v>04/03/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="E67" t="str">
-        <v>18/02/2026</v>
+        <v>07/03/2026</v>
       </c>
       <c r="F67" t="str">
         <v>-</v>
@@ -2710,21 +2710,21 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>BOVINO</v>
+        <v>BUFALO</v>
       </c>
       <c r="I67" t="str">
-        <v>CASABONA</v>
+        <v>CANCELLO ED ARNONE</v>
       </c>
       <c r="J67" t="str">
-        <v>KR</v>
+        <v>CE</v>
       </c>
       <c r="K67" t="str">
-        <v>CALABRIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>83220</v>
+        <v>84231</v>
       </c>
       <c r="B68" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -2733,10 +2733,10 @@
         <v>C</v>
       </c>
       <c r="D68" t="str">
-        <v>05/03/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="E68" t="str">
-        <v>05/02/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="F68" t="str">
         <v>-</v>
@@ -2748,10 +2748,10 @@
         <v>BOVINO</v>
       </c>
       <c r="I68" t="str">
-        <v>ALIFE</v>
+        <v>GIFFONI VALLE PIANA</v>
       </c>
       <c r="J68" t="str">
-        <v>CE</v>
+        <v>SA</v>
       </c>
       <c r="K68" t="str">
         <v>CAMPANIA</v>
@@ -2759,19 +2759,19 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>83223</v>
+        <v>85029</v>
       </c>
       <c r="B69" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C69" t="str">
         <v>C</v>
       </c>
       <c r="D69" t="str">
-        <v>11/03/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="E69" t="str">
-        <v>05/02/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="F69" t="str">
         <v>-</v>
@@ -2783,30 +2783,30 @@
         <v>BOVINO</v>
       </c>
       <c r="I69" t="str">
-        <v>SAN NICANDRO GARGANICO</v>
+        <v>SANZA</v>
       </c>
       <c r="J69" t="str">
-        <v>FG</v>
+        <v>SA</v>
       </c>
       <c r="K69" t="str">
-        <v>PUGLIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>85024</v>
+        <v>85111</v>
       </c>
       <c r="B70" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C70" t="str">
         <v>C</v>
       </c>
       <c r="D70" t="str">
-        <v>17/06/2026</v>
+        <v>26/06/2026</v>
       </c>
       <c r="E70" t="str">
-        <v>09/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="F70" t="str">
         <v>-</v>
@@ -2818,18 +2818,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I70" t="str">
-        <v>VILLETTA BARREA</v>
+        <v>CERASO</v>
       </c>
       <c r="J70" t="str">
-        <v>AQ</v>
+        <v>SA</v>
       </c>
       <c r="K70" t="str">
-        <v>ABRUZZO</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>84958</v>
+        <v>85456</v>
       </c>
       <c r="B71" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -2838,10 +2838,10 @@
         <v>C</v>
       </c>
       <c r="D71" t="str">
-        <v>29/06/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="E71" t="str">
-        <v>29/05/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="F71" t="str">
         <v>-</v>
@@ -2853,18 +2853,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I71" t="str">
-        <v>CALASCIBETTA</v>
+        <v>SANT\'ONOFRIO</v>
       </c>
       <c r="J71" t="str">
-        <v>EN</v>
+        <v>VV</v>
       </c>
       <c r="K71" t="str">
-        <v>SICILIA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>83614</v>
+        <v>85500</v>
       </c>
       <c r="B72" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -2873,33 +2873,33 @@
         <v>C</v>
       </c>
       <c r="D72" t="str">
-        <v>25/05/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="E72" t="str">
-        <v>05/03/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="F72" t="str">
         <v>-</v>
       </c>
       <c r="G72" t="str">
-        <v>Mycobacterium bovis</v>
+        <v/>
       </c>
       <c r="H72" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I72" t="str">
-        <v>CESARO\'</v>
+        <v>SAN NICANDRO GARGANICO</v>
       </c>
       <c r="J72" t="str">
-        <v>ME</v>
+        <v>FG</v>
       </c>
       <c r="K72" t="str">
-        <v>SICILIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>85234</v>
+        <v>84422</v>
       </c>
       <c r="B73" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -2908,10 +2908,10 @@
         <v>C</v>
       </c>
       <c r="D73" t="str">
-        <v>23/06/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="E73" t="str">
-        <v>22/06/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="F73" t="str">
         <v>-</v>
@@ -2923,30 +2923,30 @@
         <v>BOVINO</v>
       </c>
       <c r="I73" t="str">
-        <v>ABRIOLA</v>
+        <v>MATELICA</v>
       </c>
       <c r="J73" t="str">
-        <v>PZ</v>
+        <v>MC</v>
       </c>
       <c r="K73" t="str">
-        <v>BASILICATA</v>
+        <v>MARCHE</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>85248</v>
+        <v>83405</v>
       </c>
       <c r="B74" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C74" t="str">
         <v>C</v>
       </c>
       <c r="D74" t="str">
-        <v>06/07/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="E74" t="str">
-        <v>23/06/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="F74" t="str">
         <v>-</v>
@@ -2958,18 +2958,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I74" t="str">
-        <v>GIFFONI VALLE PIANA</v>
+        <v>CIMINNA</v>
       </c>
       <c r="J74" t="str">
-        <v>SA</v>
+        <v>PA</v>
       </c>
       <c r="K74" t="str">
-        <v>CAMPANIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>85313</v>
+        <v>84629</v>
       </c>
       <c r="B75" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -2978,45 +2978,45 @@
         <v>C</v>
       </c>
       <c r="D75" t="str">
-        <v>06/07/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="E75" t="str">
-        <v>25/06/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="F75" t="str">
         <v>-</v>
       </c>
       <c r="G75" t="str">
-        <v/>
+        <v>Mycobacterium bovis</v>
       </c>
       <c r="H75" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I75" t="str">
-        <v>LAURIA</v>
+        <v>CASTEL DI IUDICA</v>
       </c>
       <c r="J75" t="str">
-        <v>PZ</v>
+        <v>CT</v>
       </c>
       <c r="K75" t="str">
-        <v>BASILICATA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>84375</v>
+        <v>84047</v>
       </c>
       <c r="B76" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C76" t="str">
         <v>C</v>
       </c>
       <c r="D76" t="str">
-        <v>04/05/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="E76" t="str">
-        <v>23/04/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="F76" t="str">
         <v>-</v>
@@ -3028,10 +3028,10 @@
         <v>BOVINO</v>
       </c>
       <c r="I76" t="str">
-        <v>LENTINI</v>
+        <v>MODICA</v>
       </c>
       <c r="J76" t="str">
-        <v>SR</v>
+        <v>RG</v>
       </c>
       <c r="K76" t="str">
         <v>SICILIA</v>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>84320</v>
+        <v>85125</v>
       </c>
       <c r="B77" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -3048,10 +3048,10 @@
         <v>C</v>
       </c>
       <c r="D77" t="str">
-        <v>19/06/2026</v>
+        <v>17/06/2026</v>
       </c>
       <c r="E77" t="str">
-        <v>17/04/2026</v>
+        <v>17/06/2026</v>
       </c>
       <c r="F77" t="str">
         <v>-</v>
@@ -3063,18 +3063,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I77" t="str">
-        <v>PIETRAPAOLA</v>
+        <v>TROINA</v>
       </c>
       <c r="J77" t="str">
-        <v>CS</v>
+        <v>EN</v>
       </c>
       <c r="K77" t="str">
-        <v>CALABRIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>84602</v>
+        <v>83823</v>
       </c>
       <c r="B78" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -3083,10 +3083,10 @@
         <v>C</v>
       </c>
       <c r="D78" t="str">
-        <v>26/06/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="E78" t="str">
-        <v>11/03/2026</v>
+        <v>19/03/2026</v>
       </c>
       <c r="F78" t="str">
         <v>-</v>
@@ -3098,30 +3098,30 @@
         <v>BOVINO</v>
       </c>
       <c r="I78" t="str">
-        <v>CENTURIPE</v>
+        <v>BORGO SAN LORENZO</v>
       </c>
       <c r="J78" t="str">
-        <v>EN</v>
+        <v>FI</v>
       </c>
       <c r="K78" t="str">
-        <v>SICILIA</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>84629</v>
+        <v>84533</v>
       </c>
       <c r="B79" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C79" t="str">
         <v>C</v>
       </c>
       <c r="D79" t="str">
-        <v>25/06/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="E79" t="str">
-        <v>14/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="F79" t="str">
         <v>-</v>
@@ -3133,10 +3133,10 @@
         <v>BOVINO</v>
       </c>
       <c r="I79" t="str">
-        <v>CASTEL DI IUDICA</v>
+        <v>CENTURIPE</v>
       </c>
       <c r="J79" t="str">
-        <v>CT</v>
+        <v>EN</v>
       </c>
       <c r="K79" t="str">
         <v>SICILIA</v>
@@ -3144,7 +3144,7 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>84673</v>
+        <v>85719</v>
       </c>
       <c r="B80" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -3153,10 +3153,10 @@
         <v>C</v>
       </c>
       <c r="D80" t="str">
-        <v>18/05/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="E80" t="str">
-        <v>18/05/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="F80" t="str">
         <v>-</v>
@@ -3168,18 +3168,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I80" t="str">
-        <v>GIFFONI VALLE PIANA</v>
+        <v>SANT\'ONOFRIO</v>
       </c>
       <c r="J80" t="str">
-        <v>SA</v>
+        <v>VV</v>
       </c>
       <c r="K80" t="str">
-        <v>CAMPANIA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>84091</v>
+        <v>83364</v>
       </c>
       <c r="B81" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -3188,10 +3188,10 @@
         <v>C</v>
       </c>
       <c r="D81" t="str">
-        <v>16/06/2026</v>
+        <v>12/03/2026</v>
       </c>
       <c r="E81" t="str">
-        <v>07/04/2026</v>
+        <v>13/02/2026</v>
       </c>
       <c r="F81" t="str">
         <v>-</v>
@@ -3203,30 +3203,30 @@
         <v>BOVINO</v>
       </c>
       <c r="I81" t="str">
-        <v>POGGIARDO</v>
+        <v>NICOSIA</v>
       </c>
       <c r="J81" t="str">
-        <v>LE</v>
+        <v>EN</v>
       </c>
       <c r="K81" t="str">
-        <v>PUGLIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>83942</v>
+        <v>84275</v>
       </c>
       <c r="B82" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C82" t="str">
         <v>C</v>
       </c>
       <c r="D82" t="str">
-        <v>14/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="E82" t="str">
-        <v>26/03/2026</v>
+        <v>17/04/2026</v>
       </c>
       <c r="F82" t="str">
         <v>-</v>
@@ -3238,18 +3238,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I82" t="str">
-        <v>GRUMENTO NOVA</v>
+        <v>SIRACUSA</v>
       </c>
       <c r="J82" t="str">
-        <v>PZ</v>
+        <v>SR</v>
       </c>
       <c r="K82" t="str">
-        <v>BASILICATA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>84435</v>
+        <v>83227</v>
       </c>
       <c r="B83" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -3258,45 +3258,45 @@
         <v>C</v>
       </c>
       <c r="D83" t="str">
-        <v>30/04/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="E83" t="str">
-        <v>29/04/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="F83" t="str">
         <v>-</v>
       </c>
       <c r="G83" t="str">
-        <v/>
+        <v>Mycobacterium bovis</v>
       </c>
       <c r="H83" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I83" t="str">
-        <v>VOLTURARA IRPINA</v>
+        <v>ROMBIOLO</v>
       </c>
       <c r="J83" t="str">
-        <v>AV</v>
+        <v>VV</v>
       </c>
       <c r="K83" t="str">
-        <v>CAMPANIA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>83834</v>
+        <v>85031</v>
       </c>
       <c r="B84" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C84" t="str">
         <v>C</v>
       </c>
       <c r="D84" t="str">
-        <v>31/03/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="E84" t="str">
-        <v>20/03/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="F84" t="str">
         <v>-</v>
@@ -3308,18 +3308,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I84" t="str">
-        <v>VALLINFREDA</v>
+        <v>MESORACA</v>
       </c>
       <c r="J84" t="str">
-        <v>RM</v>
+        <v>KR</v>
       </c>
       <c r="K84" t="str">
-        <v>LAZIO</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>83565</v>
+        <v>84855</v>
       </c>
       <c r="B85" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -3328,10 +3328,10 @@
         <v>C</v>
       </c>
       <c r="D85" t="str">
-        <v>02/03/2026</v>
+        <v>10/06/2026</v>
       </c>
       <c r="E85" t="str">
-        <v>02/03/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="F85" t="str">
         <v>-</v>
@@ -3343,65 +3343,65 @@
         <v>BOVINO</v>
       </c>
       <c r="I85" t="str">
-        <v>FERRANDINA</v>
+        <v>PISCIOTTA</v>
       </c>
       <c r="J85" t="str">
-        <v>MT</v>
+        <v>SA</v>
       </c>
       <c r="K85" t="str">
-        <v>BASILICATA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>83628</v>
+        <v>85374</v>
       </c>
       <c r="B86" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C86" t="str">
         <v>C</v>
       </c>
       <c r="D86" t="str">
-        <v>14/04/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="E86" t="str">
-        <v>06/03/2026</v>
+        <v>26/06/2026</v>
       </c>
       <c r="F86" t="str">
         <v>-</v>
       </c>
       <c r="G86" t="str">
-        <v>Mycobacterium tuberculosis complex</v>
+        <v/>
       </c>
       <c r="H86" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I86" t="str">
-        <v>REGALBUTO</v>
+        <v>SARACENA</v>
       </c>
       <c r="J86" t="str">
-        <v>EN</v>
+        <v>CS</v>
       </c>
       <c r="K86" t="str">
-        <v>SICILIA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>84057</v>
+        <v>83774</v>
       </c>
       <c r="B87" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C87" t="str">
         <v>C</v>
       </c>
       <c r="D87" t="str">
-        <v>08/05/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="E87" t="str">
-        <v>02/04/2026</v>
+        <v>16/03/2026</v>
       </c>
       <c r="F87" t="str">
         <v>-</v>
@@ -3413,7 +3413,7 @@
         <v>BOVINO</v>
       </c>
       <c r="I87" t="str">
-        <v>AIDONE</v>
+        <v>AGIRA</v>
       </c>
       <c r="J87" t="str">
         <v>EN</v>
@@ -3424,7 +3424,7 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>84072</v>
+        <v>84668</v>
       </c>
       <c r="B88" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -3433,45 +3433,45 @@
         <v>C</v>
       </c>
       <c r="D88" t="str">
-        <v>08/04/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="E88" t="str">
-        <v>07/04/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="F88" t="str">
         <v>-</v>
       </c>
       <c r="G88" t="str">
-        <v/>
+        <v>Mycobacterium tuberculosis complex</v>
       </c>
       <c r="H88" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I88" t="str">
-        <v>TOLVE</v>
+        <v>PAZZANO</v>
       </c>
       <c r="J88" t="str">
-        <v>PZ</v>
+        <v>RC</v>
       </c>
       <c r="K88" t="str">
-        <v>BASILICATA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>83562</v>
+        <v>83190</v>
       </c>
       <c r="B89" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C89" t="str">
         <v>C</v>
       </c>
       <c r="D89" t="str">
-        <v>02/03/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="E89" t="str">
-        <v>24/02/2026</v>
+        <v>03/02/2026</v>
       </c>
       <c r="F89" t="str">
         <v>-</v>
@@ -3483,18 +3483,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I89" t="str">
-        <v>CASABONA</v>
+        <v>MODICA</v>
       </c>
       <c r="J89" t="str">
-        <v>KR</v>
+        <v>RG</v>
       </c>
       <c r="K89" t="str">
-        <v>CALABRIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>84390</v>
+        <v>85440</v>
       </c>
       <c r="B90" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -3503,10 +3503,10 @@
         <v>C</v>
       </c>
       <c r="D90" t="str">
-        <v>18/05/2026</v>
+        <v>14/07/2026</v>
       </c>
       <c r="E90" t="str">
-        <v>24/04/2026</v>
+        <v>30/06/2026</v>
       </c>
       <c r="F90" t="str">
         <v>-</v>
@@ -3518,18 +3518,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I90" t="str">
-        <v>BONIFATI</v>
+        <v>SAN NICANDRO GARGANICO</v>
       </c>
       <c r="J90" t="str">
-        <v>CS</v>
+        <v>FG</v>
       </c>
       <c r="K90" t="str">
-        <v>CALABRIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>84432</v>
+        <v>83591</v>
       </c>
       <c r="B91" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -3538,10 +3538,10 @@
         <v>C</v>
       </c>
       <c r="D91" t="str">
-        <v>27/04/2026</v>
+        <v>09/03/2026</v>
       </c>
       <c r="E91" t="str">
-        <v>24/04/2026</v>
+        <v>03/02/2026</v>
       </c>
       <c r="F91" t="str">
         <v>-</v>
@@ -3553,18 +3553,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I91" t="str">
-        <v>APRICENA</v>
+        <v>VOLTURARA IRPINA</v>
       </c>
       <c r="J91" t="str">
-        <v>FG</v>
+        <v>AV</v>
       </c>
       <c r="K91" t="str">
-        <v>PUGLIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>83527</v>
+        <v>83526</v>
       </c>
       <c r="B92" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -3573,7 +3573,7 @@
         <v>C</v>
       </c>
       <c r="D92" t="str">
-        <v>12/05/2026</v>
+        <v>04/03/2026</v>
       </c>
       <c r="E92" t="str">
         <v>18/02/2026</v>
@@ -3599,54 +3599,54 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>84361</v>
+        <v>83220</v>
       </c>
       <c r="B93" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C93" t="str">
         <v>C</v>
       </c>
       <c r="D93" t="str">
-        <v>22/05/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="E93" t="str">
-        <v>21/04/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="F93" t="str">
         <v>-</v>
       </c>
       <c r="G93" t="str">
-        <v>Mycobacterium tuberculosis complex</v>
+        <v/>
       </c>
       <c r="H93" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I93" t="str">
-        <v>SAN GIOVANNI ROTONDO</v>
+        <v>ALIFE</v>
       </c>
       <c r="J93" t="str">
-        <v>FG</v>
+        <v>CE</v>
       </c>
       <c r="K93" t="str">
-        <v>PUGLIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>84601</v>
+        <v>83223</v>
       </c>
       <c r="B94" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C94" t="str">
         <v>C</v>
       </c>
       <c r="D94" t="str">
-        <v>13/05/2026</v>
+        <v>11/03/2026</v>
       </c>
       <c r="E94" t="str">
-        <v>13/05/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="F94" t="str">
         <v>-</v>
@@ -3658,18 +3658,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I94" t="str">
-        <v>GIFFONI VALLE PIANA</v>
+        <v>SAN NICANDRO GARGANICO</v>
       </c>
       <c r="J94" t="str">
-        <v>SA</v>
+        <v>FG</v>
       </c>
       <c r="K94" t="str">
-        <v>CAMPANIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>83037</v>
+        <v>85024</v>
       </c>
       <c r="B95" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -3678,10 +3678,10 @@
         <v>C</v>
       </c>
       <c r="D95" t="str">
-        <v>02/02/2026</v>
+        <v>17/06/2026</v>
       </c>
       <c r="E95" t="str">
-        <v>19/01/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="F95" t="str">
         <v>-</v>
@@ -3693,18 +3693,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I95" t="str">
-        <v>CAGNANO VARANO</v>
+        <v>VILLETTA BARREA</v>
       </c>
       <c r="J95" t="str">
-        <v>FG</v>
+        <v>AQ</v>
       </c>
       <c r="K95" t="str">
-        <v>PUGLIA</v>
+        <v>ABRUZZO</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>83990</v>
+        <v>84958</v>
       </c>
       <c r="B96" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -3713,10 +3713,10 @@
         <v>C</v>
       </c>
       <c r="D96" t="str">
-        <v>26/03/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="E96" t="str">
-        <v>28/01/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="F96" t="str">
         <v>-</v>
@@ -3728,18 +3728,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I96" t="str">
-        <v>ROSCIGNO</v>
+        <v>CALASCIBETTA</v>
       </c>
       <c r="J96" t="str">
-        <v>SA</v>
+        <v>EN</v>
       </c>
       <c r="K96" t="str">
-        <v>CAMPANIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>82900</v>
+        <v>83614</v>
       </c>
       <c r="B97" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -3748,33 +3748,33 @@
         <v>C</v>
       </c>
       <c r="D97" t="str">
-        <v>12/01/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="E97" t="str">
-        <v>12/01/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="F97" t="str">
         <v>-</v>
       </c>
       <c r="G97" t="str">
-        <v/>
+        <v>Mycobacterium bovis</v>
       </c>
       <c r="H97" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I97" t="str">
-        <v>CELLE DI BULGHERIA</v>
+        <v>CESARO\'</v>
       </c>
       <c r="J97" t="str">
-        <v>SA</v>
+        <v>ME</v>
       </c>
       <c r="K97" t="str">
-        <v>CAMPANIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>83165</v>
+        <v>85234</v>
       </c>
       <c r="B98" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -3783,68 +3783,68 @@
         <v>C</v>
       </c>
       <c r="D98" t="str">
-        <v>20/04/2026</v>
+        <v>23/06/2026</v>
       </c>
       <c r="E98" t="str">
-        <v>29/01/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="F98" t="str">
         <v>-</v>
       </c>
       <c r="G98" t="str">
-        <v>Mycobacterium tuberculosis complex</v>
+        <v/>
       </c>
       <c r="H98" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I98" t="str">
-        <v>BRUZZANO ZEFFIRIO</v>
+        <v>ABRIOLA</v>
       </c>
       <c r="J98" t="str">
-        <v>RC</v>
+        <v>PZ</v>
       </c>
       <c r="K98" t="str">
-        <v>CALABRIA</v>
+        <v>BASILICATA</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>84022</v>
+        <v>85248</v>
       </c>
       <c r="B99" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C99" t="str">
         <v>C</v>
       </c>
       <c r="D99" t="str">
-        <v>26/05/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="E99" t="str">
-        <v>20/03/2026</v>
+        <v>23/06/2026</v>
       </c>
       <c r="F99" t="str">
         <v>-</v>
       </c>
       <c r="G99" t="str">
-        <v>Mycobacterium bovis</v>
+        <v/>
       </c>
       <c r="H99" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I99" t="str">
-        <v>CALTAGIRONE</v>
+        <v>GIFFONI VALLE PIANA</v>
       </c>
       <c r="J99" t="str">
-        <v>CT</v>
+        <v>SA</v>
       </c>
       <c r="K99" t="str">
-        <v>SICILIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>84085</v>
+        <v>85313</v>
       </c>
       <c r="B100" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -3853,45 +3853,45 @@
         <v>C</v>
       </c>
       <c r="D100" t="str">
-        <v>28/05/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="E100" t="str">
-        <v>02/04/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="F100" t="str">
         <v>-</v>
       </c>
       <c r="G100" t="str">
-        <v>Mycobacterium bovis</v>
+        <v/>
       </c>
       <c r="H100" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I100" t="str">
-        <v>BRUZZANO ZEFFIRIO</v>
+        <v>LAURIA</v>
       </c>
       <c r="J100" t="str">
-        <v>RC</v>
+        <v>PZ</v>
       </c>
       <c r="K100" t="str">
-        <v>CALABRIA</v>
+        <v>BASILICATA</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>84093</v>
+        <v>84375</v>
       </c>
       <c r="B101" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C101" t="str">
         <v>C</v>
       </c>
       <c r="D101" t="str">
-        <v>07/04/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="E101" t="str">
-        <v>07/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="F101" t="str">
         <v>-</v>
@@ -3903,30 +3903,30 @@
         <v>BOVINO</v>
       </c>
       <c r="I101" t="str">
-        <v>GIFFONI VALLE PIANA</v>
+        <v>LENTINI</v>
       </c>
       <c r="J101" t="str">
-        <v>SA</v>
+        <v>SR</v>
       </c>
       <c r="K101" t="str">
-        <v>CAMPANIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>85027</v>
+        <v>84320</v>
       </c>
       <c r="B102" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C102" t="str">
         <v>C</v>
       </c>
       <c r="D102" t="str">
-        <v>10/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="E102" t="str">
-        <v>09/06/2026</v>
+        <v>17/04/2026</v>
       </c>
       <c r="F102" t="str">
         <v>-</v>
@@ -3938,30 +3938,30 @@
         <v>BOVINO</v>
       </c>
       <c r="I102" t="str">
-        <v>MOLITERNO</v>
+        <v>PIETRAPAOLA</v>
       </c>
       <c r="J102" t="str">
-        <v>PZ</v>
+        <v>CS</v>
       </c>
       <c r="K102" t="str">
-        <v>BASILICATA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>85098</v>
+        <v>84602</v>
       </c>
       <c r="B103" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C103" t="str">
         <v>C</v>
       </c>
       <c r="D103" t="str">
-        <v>17/06/2026</v>
+        <v>26/06/2026</v>
       </c>
       <c r="E103" t="str">
-        <v>11/06/2026</v>
+        <v>11/03/2026</v>
       </c>
       <c r="F103" t="str">
         <v>-</v>
@@ -3973,18 +3973,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I103" t="str">
-        <v>BISEGNA</v>
+        <v>CENTURIPE</v>
       </c>
       <c r="J103" t="str">
-        <v>AQ</v>
+        <v>EN</v>
       </c>
       <c r="K103" t="str">
-        <v>ABRUZZO</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>85099</v>
+        <v>84673</v>
       </c>
       <c r="B104" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -3993,10 +3993,10 @@
         <v>C</v>
       </c>
       <c r="D104" t="str">
-        <v>17/06/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="E104" t="str">
-        <v>11/06/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="F104" t="str">
         <v>-</v>
@@ -4008,18 +4008,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I104" t="str">
-        <v>BISEGNA</v>
+        <v>GIFFONI VALLE PIANA</v>
       </c>
       <c r="J104" t="str">
-        <v>AQ</v>
+        <v>SA</v>
       </c>
       <c r="K104" t="str">
-        <v>ABRUZZO</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>82879</v>
+        <v>84091</v>
       </c>
       <c r="B105" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -4028,33 +4028,33 @@
         <v>C</v>
       </c>
       <c r="D105" t="str">
-        <v>22/06/2026</v>
+        <v>16/06/2026</v>
       </c>
       <c r="E105" t="str">
-        <v>16/01/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="F105" t="str">
         <v>-</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>Mycobacterium tuberculosis complex</v>
       </c>
       <c r="H105" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I105" t="str">
-        <v>RAGUSA</v>
+        <v>POGGIARDO</v>
       </c>
       <c r="J105" t="str">
-        <v>RG</v>
+        <v>LE</v>
       </c>
       <c r="K105" t="str">
-        <v>SICILIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>83835</v>
+        <v>85232</v>
       </c>
       <c r="B106" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -4063,10 +4063,10 @@
         <v>C</v>
       </c>
       <c r="D106" t="str">
-        <v>25/03/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="E106" t="str">
-        <v>20/03/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="F106" t="str">
         <v>-</v>
@@ -4078,18 +4078,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I106" t="str">
-        <v>SPILINGA</v>
+        <v>GIFFONI VALLE PIANA</v>
       </c>
       <c r="J106" t="str">
-        <v>VV</v>
+        <v>SA</v>
       </c>
       <c r="K106" t="str">
-        <v>CALABRIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>85331</v>
+        <v>84435</v>
       </c>
       <c r="B107" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -4098,10 +4098,10 @@
         <v>C</v>
       </c>
       <c r="D107" t="str">
-        <v>25/06/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="E107" t="str">
-        <v>13/06/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="F107" t="str">
         <v>-</v>
@@ -4113,18 +4113,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I107" t="str">
-        <v>UMBRIATICO</v>
+        <v>VOLTURARA IRPINA</v>
       </c>
       <c r="J107" t="str">
-        <v>KR</v>
+        <v>AV</v>
       </c>
       <c r="K107" t="str">
-        <v>CALABRIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>83991</v>
+        <v>84057</v>
       </c>
       <c r="B108" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -4133,10 +4133,10 @@
         <v>C</v>
       </c>
       <c r="D108" t="str">
-        <v>26/03/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="E108" t="str">
-        <v>28/01/2026</v>
+        <v>02/04/2026</v>
       </c>
       <c r="F108" t="str">
         <v>-</v>
@@ -4148,18 +4148,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I108" t="str">
-        <v>ROSCIGNO</v>
+        <v>AIDONE</v>
       </c>
       <c r="J108" t="str">
-        <v>SA</v>
+        <v>EN</v>
       </c>
       <c r="K108" t="str">
-        <v>CAMPANIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>84226</v>
+        <v>84082</v>
       </c>
       <c r="B109" t="str">
         <v>RISCONTRO ANATOMO-PATOLOGICO</v>
@@ -4168,33 +4168,418 @@
         <v>C</v>
       </c>
       <c r="D109" t="str">
-        <v>06/05/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="E109" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="F109" t="str">
+        <v>-</v>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I109" t="str">
+        <v>CANCELLO ED ARNONE</v>
+      </c>
+      <c r="J109" t="str">
+        <v>CE</v>
+      </c>
+      <c r="K109" t="str">
+        <v>CAMPANIA</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>83565</v>
+      </c>
+      <c r="B110" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C110" t="str">
+        <v>C</v>
+      </c>
+      <c r="D110" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="E110" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="F110" t="str">
+        <v>-</v>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I110" t="str">
+        <v>FERRANDINA</v>
+      </c>
+      <c r="J110" t="str">
+        <v>MT</v>
+      </c>
+      <c r="K110" t="str">
+        <v>BASILICATA</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>83628</v>
+      </c>
+      <c r="B111" t="str">
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+      </c>
+      <c r="C111" t="str">
+        <v>C</v>
+      </c>
+      <c r="D111" t="str">
         <v>14/04/2026</v>
       </c>
-      <c r="F109" t="str">
-        <v>-</v>
-      </c>
-      <c r="G109" t="str">
-        <v/>
-      </c>
-      <c r="H109" t="str">
-        <v>BOVINO</v>
-      </c>
-      <c r="I109" t="str">
-        <v>MORETTA</v>
-      </c>
-      <c r="J109" t="str">
-        <v>CN</v>
-      </c>
-      <c r="K109" t="str">
-        <v>PIEMONTE</v>
+      <c r="E111" t="str">
+        <v>06/03/2026</v>
+      </c>
+      <c r="F111" t="str">
+        <v>-</v>
+      </c>
+      <c r="G111" t="str">
+        <v>Mycobacterium tuberculosis complex</v>
+      </c>
+      <c r="H111" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I111" t="str">
+        <v>REGALBUTO</v>
+      </c>
+      <c r="J111" t="str">
+        <v>EN</v>
+      </c>
+      <c r="K111" t="str">
+        <v>SICILIA</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>85320</v>
+      </c>
+      <c r="B112" t="str">
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+      </c>
+      <c r="C112" t="str">
+        <v>C</v>
+      </c>
+      <c r="D112" t="str">
+        <v>10/07/2026</v>
+      </c>
+      <c r="E112" t="str">
+        <v>26/06/2026</v>
+      </c>
+      <c r="F112" t="str">
+        <v>-</v>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I112" t="str">
+        <v>GIFFONI SEI CASALI</v>
+      </c>
+      <c r="J112" t="str">
+        <v>SA</v>
+      </c>
+      <c r="K112" t="str">
+        <v>CAMPANIA</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>83562</v>
+      </c>
+      <c r="B113" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C113" t="str">
+        <v>C</v>
+      </c>
+      <c r="D113" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="E113" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="F113" t="str">
+        <v>-</v>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I113" t="str">
+        <v>CASABONA</v>
+      </c>
+      <c r="J113" t="str">
+        <v>KR</v>
+      </c>
+      <c r="K113" t="str">
+        <v>CALABRIA</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>84390</v>
+      </c>
+      <c r="B114" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C114" t="str">
+        <v>C</v>
+      </c>
+      <c r="D114" t="str">
+        <v>18/05/2026</v>
+      </c>
+      <c r="E114" t="str">
+        <v>24/04/2026</v>
+      </c>
+      <c r="F114" t="str">
+        <v>-</v>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I114" t="str">
+        <v>BONIFATI</v>
+      </c>
+      <c r="J114" t="str">
+        <v>CS</v>
+      </c>
+      <c r="K114" t="str">
+        <v>CALABRIA</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>84432</v>
+      </c>
+      <c r="B115" t="str">
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+      </c>
+      <c r="C115" t="str">
+        <v>C</v>
+      </c>
+      <c r="D115" t="str">
+        <v>27/04/2026</v>
+      </c>
+      <c r="E115" t="str">
+        <v>24/04/2026</v>
+      </c>
+      <c r="F115" t="str">
+        <v>-</v>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I115" t="str">
+        <v>APRICENA</v>
+      </c>
+      <c r="J115" t="str">
+        <v>FG</v>
+      </c>
+      <c r="K115" t="str">
+        <v>PUGLIA</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>83527</v>
+      </c>
+      <c r="B116" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C116" t="str">
+        <v>C</v>
+      </c>
+      <c r="D116" t="str">
+        <v>12/05/2026</v>
+      </c>
+      <c r="E116" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="F116" t="str">
+        <v>-</v>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I116" t="str">
+        <v>CASABONA</v>
+      </c>
+      <c r="J116" t="str">
+        <v>KR</v>
+      </c>
+      <c r="K116" t="str">
+        <v>CALABRIA</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>84361</v>
+      </c>
+      <c r="B117" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C117" t="str">
+        <v>C</v>
+      </c>
+      <c r="D117" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="E117" t="str">
+        <v>21/04/2026</v>
+      </c>
+      <c r="F117" t="str">
+        <v>-</v>
+      </c>
+      <c r="G117" t="str">
+        <v>Mycobacterium tuberculosis complex</v>
+      </c>
+      <c r="H117" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I117" t="str">
+        <v>SAN GIOVANNI ROTONDO</v>
+      </c>
+      <c r="J117" t="str">
+        <v>FG</v>
+      </c>
+      <c r="K117" t="str">
+        <v>PUGLIA</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>84601</v>
+      </c>
+      <c r="B118" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C118" t="str">
+        <v>C</v>
+      </c>
+      <c r="D118" t="str">
+        <v>13/05/2026</v>
+      </c>
+      <c r="E118" t="str">
+        <v>13/05/2026</v>
+      </c>
+      <c r="F118" t="str">
+        <v>-</v>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I118" t="str">
+        <v>GIFFONI VALLE PIANA</v>
+      </c>
+      <c r="J118" t="str">
+        <v>SA</v>
+      </c>
+      <c r="K118" t="str">
+        <v>CAMPANIA</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>83037</v>
+      </c>
+      <c r="B119" t="str">
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+      </c>
+      <c r="C119" t="str">
+        <v>C</v>
+      </c>
+      <c r="D119" t="str">
+        <v>02/02/2026</v>
+      </c>
+      <c r="E119" t="str">
+        <v>19/01/2026</v>
+      </c>
+      <c r="F119" t="str">
+        <v>-</v>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I119" t="str">
+        <v>CAGNANO VARANO</v>
+      </c>
+      <c r="J119" t="str">
+        <v>FG</v>
+      </c>
+      <c r="K119" t="str">
+        <v>PUGLIA</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>83990</v>
+      </c>
+      <c r="B120" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C120" t="str">
+        <v>C</v>
+      </c>
+      <c r="D120" t="str">
+        <v>26/03/2026</v>
+      </c>
+      <c r="E120" t="str">
+        <v>28/01/2026</v>
+      </c>
+      <c r="F120" t="str">
+        <v>-</v>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I120" t="str">
+        <v>ROSCIGNO</v>
+      </c>
+      <c r="J120" t="str">
+        <v>SA</v>
+      </c>
+      <c r="K120" t="str">
+        <v>CAMPANIA</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K120"/>
   </ignoredErrors>
 </worksheet>
 </file>